--- a/ClosedXML.Tests/Resource/Examples/Tables/UsingTables.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Tables/UsingTables.xlsx
@@ -74,10 +74,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="0" formatCode=""/>
     <x:numFmt numFmtId="164" formatCode="$ #,##0"/>
-    <x:numFmt numFmtId="165" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -338,7 +337,7 @@
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -411,7 +410,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -427,7 +426,7 @@
       <x:numFmt numFmtId="164" formatCode="$ #,##0"/>
     </x:dxf>
     <x:dxf>
-      <x:numFmt numFmtId="165" formatCode="0.00"/>
+      <x:numFmt numFmtId="2" formatCode="0.00"/>
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
